--- a/human_resources_forms/002_workplace_harassment_complaint_form--human_resources_forms.xlsx
+++ b/human_resources_forms/002_workplace_harassment_complaint_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>witness_list</t>
+          <t>witness_list_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Was there a witness</t>
+          <t>Witness List 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>witness_names</t>
+          <t>witness_names_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Who were they?</t>
+          <t>Witness Names 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>witness_statement</t>
+          <t>witness_statement_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What did they say</t>
+          <t>Witness Statement 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>resolution</t>
+          <t>resolution_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Was the issue resolved</t>
+          <t>Resolution 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -871,7 +871,7 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -964,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>witness_list_choices</t>
+          <t>witness_list_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>witness_list_choices</t>
+          <t>witness_list_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>witness_names_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>witness_names_choices</t>
+          <t>witness_names_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>resolution_choices</t>
+          <t>resolution_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>resolution_choices</t>
+          <t>resolution_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
